--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:29</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>1/15</t>
         </is>
       </c>
     </row>
@@ -776,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -945,22 +953,22 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -993,12 +1001,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1012,7 +1020,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1048,7 +1056,1343 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>1/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -862,32 +862,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:25</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -919,33 +923,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -973,32 +981,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1006,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1030,33 +1042,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1084,32 +1100,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1117,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1141,33 +1161,37 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1228,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1278,7 +1302,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1306,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1339,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1363,33 +1391,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1450,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1500,7 +1532,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1561,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1611,7 +1643,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1672,7 +1704,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1711,7 +1743,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1722,7 +1754,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1783,7 +1815,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:10</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1833,7 +1865,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1841,22 +1873,22 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1889,12 +1921,12 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1944,7 +1976,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1952,22 +1984,22 @@
       <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2000,12 +2032,12 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2019,7 +2051,7 @@
       <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -2055,7 +2087,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2116,7 +2148,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2166,7 +2198,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2259,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2277,7 +2309,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2285,22 +2317,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A53629D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2333,12 +2365,12 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2352,47 +2384,1062 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>08:03</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W18" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X17" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y17" s="2" t="inlineStr">
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z17" s="2" t="inlineStr">
+      <c r="Z18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
+      <c r="AA18" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB17" s="2" t="inlineStr">
+      <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>79.0</t>
         </is>
       </c>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>1/15</t>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr"/>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC26"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1340,24 +1340,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1593,7 +1593,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1671,32 +1671,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:43</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1704,7 +1708,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1728,17 +1732,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1748,13 +1752,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1823,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1926,7 +1934,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2037,7 +2045,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2259,7 +2267,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2370,7 +2378,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2489,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2604,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,7 +2715,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2761,7 +2769,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2830,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2861,7 +2869,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2987,7 +2995,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3159,7 +3167,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3213,7 +3221,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3274,7 +3282,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3323,7 +3331,7 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3336,22 +3344,22 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -3384,12 +3392,12 @@
       <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3403,7 +3411,7 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3440,6 +3448,121 @@
       <c r="AC26" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1560,32 +1560,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:07</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>117分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1593,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1617,33 +1621,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1681,24 +1689,24 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:43</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1708,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1757,7 +1765,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1823,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1862,7 +1870,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1901,32 +1909,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -1934,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1958,33 +1970,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2012,32 +2028,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -2045,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2069,33 +2089,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2234,32 +2258,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2267,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2291,33 +2319,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2410,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2489,7 +2521,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2604,7 +2636,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2643,7 +2675,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2715,7 +2747,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2769,7 +2801,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2830,7 +2862,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2941,7 +2973,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3056,7 +3088,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3095,7 +3127,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3167,7 +3199,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3221,7 +3253,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3282,7 +3314,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3354,7 +3386,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3397,7 +3429,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3411,7 +3443,7 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3455,22 +3487,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3503,12 +3535,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3522,47 +3554,1062 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>09:05</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W28" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z28" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr"/>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="AC27" s="2" t="inlineStr">
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
         <is>
           <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>117.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr"/>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,14 +1406,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>91.0</t>
@@ -1421,7 +1421,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1521,7 +1521,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1946,7 +1946,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2065,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2119,7 +2119,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2349,7 +2349,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2488,32 +2488,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2521,7 +2525,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2545,17 +2549,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2565,17 +2569,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2603,32 +2607,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2636,7 +2644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2660,17 +2668,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2680,13 +2688,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2714,32 +2726,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2747,7 +2763,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2771,37 +2787,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2862,7 +2878,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2906,13 +2922,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB21" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2993,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3012,7 +3032,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3027,7 +3047,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3088,7 +3108,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3219,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3238,7 +3258,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3253,7 +3273,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3281,32 +3301,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3314,7 +3338,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3338,29 +3362,29 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>91.0</t>
@@ -3368,7 +3392,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3396,32 +3420,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
@@ -3429,7 +3457,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3453,17 +3481,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3473,13 +3501,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3572,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,7 +3683,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3690,7 +3722,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3729,32 +3761,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3762,7 +3798,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3786,37 +3822,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3877,7 +3913,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3931,7 +3967,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4028,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4103,7 +4139,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4157,7 +4193,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4254,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4272,7 +4308,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4333,7 +4369,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4377,13 +4413,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4484,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4498,7 +4538,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4506,22 +4546,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4554,12 +4594,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4573,41 +4613,727 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB36" s="2" t="inlineStr"/>
-      <c r="AC36" s="2" t="inlineStr">
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
         </is>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,18 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -953,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,7 +1410,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1421,7 +1425,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1597,7 +1601,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,17 +1645,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1720,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1770,7 +1774,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1870,18 +1874,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1946,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1985,22 +1993,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2104,22 +2112,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2303,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2334,22 +2342,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2579,7 +2587,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2652,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2688,17 +2696,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2771,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2802,22 +2810,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2932,7 +2940,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2993,7 +3001,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3047,7 +3055,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3108,7 +3116,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3147,18 +3155,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3219,7 +3231,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3258,7 +3270,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3273,7 +3285,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3350,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3377,7 +3389,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3392,7 +3404,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3511,7 +3523,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3695,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3798,7 +3810,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3852,7 +3864,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3880,32 +3892,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3913,7 +3929,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3937,17 +3953,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -3957,17 +3973,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3995,32 +4011,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -4028,7 +4048,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4052,33 +4072,37 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB31" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4106,32 +4130,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -4139,7 +4167,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4163,37 +4191,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4221,32 +4249,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -4254,7 +4286,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4278,37 +4310,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4336,32 +4368,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4369,7 +4405,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4393,17 +4429,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4413,17 +4449,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4451,32 +4487,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4484,7 +4524,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4508,37 +4548,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4566,32 +4606,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4599,7 +4643,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4623,37 +4667,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4714,7 +4758,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4768,7 +4812,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4796,32 +4840,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4829,7 +4877,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4853,33 +4901,37 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB38" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4940,7 +4992,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -4979,7 +5031,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -4994,7 +5046,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5055,7 +5107,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5109,7 +5161,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5170,7 +5222,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5209,7 +5261,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5224,7 +5276,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5232,22 +5284,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5280,12 +5332,12 @@
       <c r="M42" s="2" t="inlineStr"/>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5329,13 +5381,933 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>93.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB42" s="2" t="inlineStr"/>
-      <c r="AC42" s="2" t="inlineStr">
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC50"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,18 +1525,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1659,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1778,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,22 +1878,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1993,22 +1997,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2112,7 +2116,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2127,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2342,22 +2346,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2771,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2825,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2944,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3059,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3116,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3170,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3275,12 +3279,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3350,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3394,17 +3398,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3527,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3695,7 +3699,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3734,18 +3738,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB28" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3864,7 +3872,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3983,7 +3991,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4087,22 +4095,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4206,7 +4214,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4221,7 +4229,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4286,7 +4294,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4325,22 +4333,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4467,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4524,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4563,22 +4571,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4697,7 +4705,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4812,7 +4820,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4862,12 +4870,12 @@
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4877,7 +4885,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4931,7 +4939,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4959,32 +4967,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4992,7 +5004,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5016,17 +5028,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5036,17 +5048,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5161,7 +5173,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5189,32 +5201,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5222,7 +5238,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5246,17 +5262,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5266,12 +5282,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5304,32 +5320,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -5337,7 +5357,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5361,37 +5381,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5419,32 +5439,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5452,7 +5476,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5476,33 +5500,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB43" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5530,32 +5558,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -5563,7 +5595,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5587,37 +5619,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5645,32 +5677,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5678,7 +5714,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5702,37 +5738,37 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5829,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5832,7 +5868,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5847,7 +5883,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5908,7 +5944,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5962,7 +5998,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6059,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6077,7 +6113,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6138,7 +6174,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6182,12 +6218,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>93.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6253,7 +6289,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6297,17 +6333,592 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB50" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
-      <c r="AC50" s="2" t="inlineStr">
-        <is>
-          <t>8/18</t>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>88.5</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,22 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1410,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,17 +2121,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,14 +2576,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>88.5</t>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,22 +2814,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2944,7 +2944,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3159,22 +3159,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3235,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3274,22 +3274,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3354,7 +3354,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3393,22 +3393,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3743,12 +3743,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4175,7 +4175,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4219,17 +4219,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4294,7 +4294,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4467,7 +4467,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4690,22 +4690,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4820,7 +4820,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4885,7 +4885,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4924,22 +4924,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5004,7 +5004,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5043,22 +5043,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5277,22 +5277,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5357,7 +5357,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5411,7 +5411,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5520,12 +5520,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5687,24 +5687,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5763,12 +5763,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5796,32 +5796,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -5829,7 +5833,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5853,17 +5857,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5873,17 +5877,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5911,32 +5915,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5944,7 +5952,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5968,37 +5976,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6026,32 +6034,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6059,7 +6071,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6083,37 +6095,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6141,32 +6153,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6174,7 +6190,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6198,37 +6214,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>93.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6256,32 +6272,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6289,7 +6309,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6313,37 +6333,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6371,32 +6391,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6404,7 +6428,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6428,17 +6452,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6448,12 +6472,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6519,7 +6543,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6573,7 +6597,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6658,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6688,7 +6712,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6749,7 +6773,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6798,12 +6822,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6864,7 +6888,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6908,17 +6932,592 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB55" s="2" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="AC55" s="2" t="inlineStr">
-        <is>
-          <t>13/18</t>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -952,12 +952,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,22 +1997,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2837,22 +2837,22 @@
       <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>08:21</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2885,12 +2885,12 @@
       <c r="M21" s="2" t="inlineStr"/>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2904,7 +2904,7 @@
       <c r="T21" s="2" t="inlineStr"/>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2952,22 +2952,22 @@
       <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>08:30</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -3000,12 +3000,12 @@
       <c r="M22" s="2" t="inlineStr"/>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3019,7 +3019,7 @@
       <c r="T22" s="2" t="inlineStr"/>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -3044,22 +3044,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       <c r="T23" s="2" t="inlineStr"/>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>08:31</t>
+          <t>08:33</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
@@ -3164,17 +3164,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3182,60 +3182,64 @@
       <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>08:33</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3249,7 +3253,7 @@
       <c r="T24" s="2" t="inlineStr"/>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>08:33</t>
+          <t>08:45</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3259,17 +3263,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3279,17 +3283,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3297,24 +3301,24 @@
       <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A36930D</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>08:45</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3327,34 +3331,34 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>91分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3368,7 +3372,7 @@
       <c r="T25" s="2" t="inlineStr"/>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>08:45</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3393,22 +3397,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3420,7 @@
       <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>沪A36930D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -3426,7 +3430,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -3436,44 +3440,40 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:21</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3487,7 +3487,7 @@
       <c r="T26" s="2" t="inlineStr"/>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3497,17 +3497,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3517,17 +3517,13 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr">
-        <is>
-          <t>87.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -3535,7 +3531,7 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -3545,7 +3541,7 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
@@ -3583,12 +3579,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3602,7 +3598,7 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>08:57</t>
+          <t>09:05</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3627,18 +3623,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3646,60 +3646,64 @@
       <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>09:05</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3713,7 +3717,7 @@
       <c r="T28" s="2" t="inlineStr"/>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>09:05</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
@@ -3723,22 +3727,22 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3748,12 +3752,12 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3761,24 +3765,24 @@
       <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A55207D</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -3791,24 +3795,24 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3818,7 +3822,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3857,7 +3861,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3867,12 +3871,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3880,7 +3884,7 @@
       <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -3890,7 +3894,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -3910,34 +3914,34 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>10:41</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3951,7 +3955,7 @@
       <c r="T30" s="2" t="inlineStr"/>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -3976,22 +3980,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3999,7 +4003,7 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -4009,7 +4013,7 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
@@ -4029,34 +4033,34 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>10:41</t>
+          <t>10:54</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4070,7 +4074,7 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -4100,17 +4104,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4118,24 +4122,24 @@
       <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4148,34 +4152,34 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4214,22 +4218,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4237,24 +4241,24 @@
       <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A58633D</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>09:30</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4267,34 +4271,34 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>10:55</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4308,7 +4312,7 @@
       <c r="T33" s="2" t="inlineStr"/>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
@@ -4333,22 +4337,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4356,24 +4360,24 @@
       <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>09:45</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4386,34 +4390,34 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4427,7 +4431,7 @@
       <c r="T34" s="2" t="inlineStr"/>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
@@ -4452,22 +4456,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4475,24 +4479,24 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4505,34 +4509,34 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4546,7 +4550,7 @@
       <c r="T35" s="2" t="inlineStr"/>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
@@ -4571,22 +4575,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4598,7 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -4604,7 +4608,7 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
@@ -4614,36 +4618,32 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4665,7 +4665,7 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
@@ -4675,37 +4675,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4713,60 +4713,64 @@
       <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4790,37 +4794,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4828,24 +4832,24 @@
       <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -4858,34 +4862,34 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4899,7 +4903,7 @@
       <c r="T38" s="2" t="inlineStr"/>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
@@ -4929,17 +4933,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4947,7 +4951,7 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -4957,7 +4961,7 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
@@ -4967,44 +4971,40 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5018,7 +5018,7 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
@@ -5028,37 +5028,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5066,60 +5066,64 @@
       <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>沪A51173D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5143,37 +5147,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5181,24 +5185,24 @@
       <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>10:45</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5211,34 +5215,34 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5252,7 +5256,7 @@
       <c r="T41" s="2" t="inlineStr"/>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
@@ -5282,12 +5286,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5300,24 +5304,24 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5330,34 +5334,34 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5401,17 +5405,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5419,7 +5423,7 @@
       <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -5429,7 +5433,7 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
@@ -5449,7 +5453,7 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>12:29</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
@@ -5471,12 +5475,12 @@
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5490,7 +5494,7 @@
       <c r="T43" s="2" t="inlineStr"/>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
@@ -5525,12 +5529,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5538,24 +5542,24 @@
       <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5568,34 +5572,34 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:29</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5609,7 +5613,7 @@
       <c r="T44" s="2" t="inlineStr"/>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
@@ -5639,17 +5643,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5657,24 +5661,24 @@
       <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5687,34 +5691,34 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5728,7 +5732,7 @@
       <c r="T45" s="2" t="inlineStr"/>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
@@ -5763,12 +5767,12 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5776,24 +5780,24 @@
       <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>11:35</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5806,12 +5810,12 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
@@ -5828,12 +5832,12 @@
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5847,7 +5851,7 @@
       <c r="T46" s="2" t="inlineStr"/>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
@@ -5872,22 +5876,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5895,24 +5899,24 @@
       <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D47" s="2" t="inlineStr">
-        <is>
-          <t>11:50</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -5925,12 +5929,12 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
@@ -5947,12 +5951,12 @@
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5966,7 +5970,7 @@
       <c r="T47" s="2" t="inlineStr"/>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
@@ -5996,17 +6000,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6014,24 +6018,24 @@
       <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6044,34 +6048,34 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6085,7 +6089,7 @@
       <c r="T48" s="2" t="inlineStr"/>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
@@ -6115,17 +6119,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6133,24 +6137,24 @@
       <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>12:15</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6163,34 +6167,34 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>75分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6204,7 +6208,7 @@
       <c r="T49" s="2" t="inlineStr"/>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
@@ -6234,17 +6238,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6252,24 +6256,24 @@
       <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6282,24 +6286,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6309,7 +6313,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6323,7 +6327,7 @@
       <c r="T50" s="2" t="inlineStr"/>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
@@ -6348,22 +6352,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6371,24 +6375,24 @@
       <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>沪A52736D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
-      <c r="D51" s="2" t="inlineStr">
-        <is>
-          <t>12:40</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
-        </is>
-      </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
           <t>全程车</t>
@@ -6401,12 +6405,12 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
@@ -6423,12 +6427,12 @@
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6442,7 +6446,7 @@
       <c r="T51" s="2" t="inlineStr"/>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
@@ -6467,22 +6471,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6490,22 +6494,22 @@
       <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
-        <is>
-          <t>12:50</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -6543,7 +6547,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6557,7 +6561,7 @@
       <c r="T52" s="2" t="inlineStr"/>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>13:05</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
@@ -6587,17 +6591,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6605,22 +6609,22 @@
       <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A57022D</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -6653,12 +6657,12 @@
       <c r="M53" s="2" t="inlineStr"/>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6672,7 +6676,7 @@
       <c r="T53" s="2" t="inlineStr"/>
       <c r="U53" s="2" t="inlineStr">
         <is>
-          <t>13:05</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="V53" s="2" t="inlineStr">
@@ -6702,17 +6706,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6720,22 +6724,22 @@
       <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A35172D</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -6768,12 +6772,12 @@
       <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6787,7 +6791,7 @@
       <c r="T54" s="2" t="inlineStr"/>
       <c r="U54" s="2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="V54" s="2" t="inlineStr">
@@ -6822,12 +6826,12 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6835,22 +6839,22 @@
       <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -6883,12 +6887,12 @@
       <c r="M55" s="2" t="inlineStr"/>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6902,7 +6906,7 @@
       <c r="T55" s="2" t="inlineStr"/>
       <c r="U55" s="2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="V55" s="2" t="inlineStr">
@@ -6927,22 +6931,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6950,22 +6954,22 @@
       <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A59117D</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>13:40</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -6998,12 +7002,12 @@
       <c r="M56" s="2" t="inlineStr"/>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7017,7 +7021,7 @@
       <c r="T56" s="2" t="inlineStr"/>
       <c r="U56" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:55</t>
         </is>
       </c>
       <c r="V56" s="2" t="inlineStr">
@@ -7047,17 +7051,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7065,22 +7069,22 @@
       <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -7113,12 +7117,12 @@
       <c r="M57" s="2" t="inlineStr"/>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7132,7 +7136,7 @@
       <c r="T57" s="2" t="inlineStr"/>
       <c r="U57" s="2" t="inlineStr">
         <is>
-          <t>13:55</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="V57" s="2" t="inlineStr">
@@ -7162,17 +7166,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7180,22 +7184,22 @@
       <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -7228,12 +7232,12 @@
       <c r="M58" s="2" t="inlineStr"/>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7247,7 +7251,7 @@
       <c r="T58" s="2" t="inlineStr"/>
       <c r="U58" s="2" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="V58" s="2" t="inlineStr">
@@ -7277,17 +7281,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7295,22 +7299,22 @@
       <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>沪A35186D</t>
+          <t>沪A55150D</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -7343,12 +7347,12 @@
       <c r="M59" s="2" t="inlineStr"/>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7387,22 +7391,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7410,22 +7414,22 @@
       <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>沪A55150D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>14:20</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7458,12 +7462,12 @@
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7477,7 +7481,7 @@
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="V60" s="2" t="inlineStr">
@@ -7502,22 +7506,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC60"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,12 +1878,12 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2007,12 +2007,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,17 +2121,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2351,17 +2351,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3059,7 +3059,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3584,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3623,7 +3623,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3633,12 +3633,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3941,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4104,17 +4104,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4228,12 +4228,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4461,17 +4461,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4889,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5291,12 +5291,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5519,12 +5519,12 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5534,7 +5534,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5643,17 +5643,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5762,17 +5762,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5891,7 +5891,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5956,7 +5956,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6286,24 +6286,24 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6405,24 +6405,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:21</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6514,32 +6514,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6547,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6571,27 +6575,27 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6601,7 +6605,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6629,32 +6633,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6662,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6686,17 +6694,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6706,17 +6714,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6744,32 +6752,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -6777,7 +6789,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6801,17 +6813,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6821,17 +6833,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6892,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6946,7 +6958,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7007,7 +7019,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7122,7 +7134,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7176,7 +7188,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7237,7 +7249,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7352,7 +7364,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7406,7 +7418,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7414,22 +7426,22 @@
       <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>沪A35591D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>14:45</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -7462,12 +7474,12 @@
       <c r="M60" s="2" t="inlineStr"/>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7481,47 +7493,388 @@
       <c r="T60" s="2" t="inlineStr"/>
       <c r="U60" s="2" t="inlineStr">
         <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
           <t>14:45</t>
         </is>
       </c>
-      <c r="V60" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W60" s="2" t="inlineStr">
+      <c r="W61" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X60" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y60" s="2" t="inlineStr">
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z60" s="2" t="inlineStr">
+      <c r="Z61" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
+      <c r="AA61" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB60" s="2" t="inlineStr">
-        <is>
-          <t>87.5</t>
-        </is>
-      </c>
-      <c r="AC60" s="2" t="inlineStr">
-        <is>
-          <t>8/18</t>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr"/>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,12 +828,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2121,17 +2121,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2346,14 +2346,14 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3990,12 +3990,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4104,17 +4104,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4456,14 +4456,14 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4814,12 +4814,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4889,7 +4889,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5123,7 +5123,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5242,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5529,12 +5529,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5599,7 +5599,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5638,14 +5638,14 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -5653,7 +5653,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5718,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5762,17 +5762,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5881,12 +5881,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6129,7 +6129,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6313,7 +6313,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6524,24 +6524,24 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6600,12 +6600,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6670,7 +6670,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6709,14 +6709,14 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
           <t>88.0</t>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6752,36 +6752,32 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>76分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -6789,7 +6785,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6813,17 +6809,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6833,17 +6829,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6871,32 +6867,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6904,7 +6904,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>79.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7479,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7594,7 +7594,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7758,12 +7758,12 @@
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7878,6 +7878,347 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr"/>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC66"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -947,17 +947,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1605,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2192,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2591,7 +2591,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,14 +2695,14 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
           <t>88.5</t>
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2814,17 +2814,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2929,7 +2929,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3044,7 +3044,7 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
@@ -3054,7 +3054,7 @@
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3164,17 +3164,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3283,12 +3283,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3473,7 +3473,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3822,7 +3822,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3941,7 +3941,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4099,7 +4099,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4179,7 +4179,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4298,7 +4298,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4337,14 +4337,14 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
           <t>88.5</t>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4536,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4575,17 +4575,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4618,12 +4618,12 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程40%处后消失；随后反向物理轨迹由seq24推进至seq37，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4659,10 +4659,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q36" s="2" t="inlineStr"/>
-      <c r="R36" s="2" t="inlineStr"/>
+      <c r="Q36" s="2" t="inlineStr">
+        <is>
+          <t>五莲路东陆路</t>
+        </is>
+      </c>
+      <c r="R36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
       <c r="S36" s="2" t="inlineStr"/>
-      <c r="T36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq17映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4690,7 +4702,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4770,7 +4782,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4809,7 +4821,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4819,7 +4831,7 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4889,7 +4901,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4933,12 +4945,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5004,7 +5016,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5123,7 +5135,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5167,17 +5179,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5242,7 +5254,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5361,7 +5373,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5480,7 +5492,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5599,7 +5611,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5653,7 +5665,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5718,7 +5730,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5757,7 +5769,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5837,7 +5849,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5876,7 +5888,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -5886,7 +5898,7 @@
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5956,7 +5968,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -5995,17 +6007,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6075,7 +6087,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6119,17 +6131,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6194,7 +6206,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6238,12 +6250,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6313,7 +6325,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6432,7 +6444,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6551,7 +6563,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6670,7 +6682,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6724,7 +6736,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6785,7 +6797,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6824,7 +6836,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6877,24 +6889,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6904,7 +6916,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6943,7 +6955,7 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
@@ -6953,7 +6965,7 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>79.7</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -6986,32 +6998,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7019,7 +7035,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7043,32 +7059,32 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7101,32 +7117,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7134,7 +7154,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7158,17 +7178,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7178,17 +7198,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7216,32 +7236,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7249,7 +7273,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7273,17 +7297,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7293,12 +7317,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7364,7 +7388,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7418,7 +7442,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7479,7 +7503,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7594,7 +7618,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7709,7 +7733,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7824,7 +7848,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7935,7 +7959,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8046,7 +8070,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8161,7 +8185,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8215,7 +8239,693 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr"/>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>80.3</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,18 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1371,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1410,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1763,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1839,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1878,17 +1882,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1958,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1997,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2131,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2231,7 +2235,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2307,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2346,17 +2350,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2422,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2537,7 +2541,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2576,22 +2580,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2660,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2710,7 +2714,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2779,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2829,7 +2833,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2894,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2944,7 +2948,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3005,7 +3009,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3059,7 +3063,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3120,7 +3124,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3159,7 +3163,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3174,7 +3178,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3243,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3278,22 +3282,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3412,7 +3416,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3477,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3512,18 +3516,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3592,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3623,22 +3631,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3703,7 +3711,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3742,7 +3750,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3822,7 +3830,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3876,7 +3884,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3941,7 +3949,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3980,17 +3988,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4060,7 +4068,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4114,7 +4122,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4218,22 +4226,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4306,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4352,7 +4360,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4425,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4456,17 +4464,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4536,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4590,7 +4598,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4651,7 +4659,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4717,7 +4725,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4782,7 +4790,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4836,7 +4844,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4909,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4940,22 +4948,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4983,12 +4991,12 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程48%处后消失；随后反向物理轨迹由seq25推进至seq34，推进9站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -5016,7 +5024,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5024,10 +5032,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q39" s="2" t="inlineStr"/>
-      <c r="R39" s="2" t="inlineStr"/>
+      <c r="Q39" s="2" t="inlineStr">
+        <is>
+          <t>巨峰路五莲路</t>
+        </is>
+      </c>
+      <c r="R39" s="2" t="inlineStr">
+        <is>
+          <t>11:21</t>
+        </is>
+      </c>
       <c r="S39" s="2" t="inlineStr"/>
-      <c r="T39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq20映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5055,7 +5075,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5135,7 +5155,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5174,7 +5194,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5189,7 +5209,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5254,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5293,22 +5313,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5373,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5412,22 +5432,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5492,7 +5512,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5531,17 +5551,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5611,7 +5631,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5650,17 +5670,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5730,7 +5750,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5784,7 +5804,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5849,7 +5869,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5903,7 +5923,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6022,7 +6042,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6087,7 +6107,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6126,7 +6146,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6141,7 +6161,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6206,7 +6226,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6245,22 +6265,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6345,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6364,22 +6384,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6444,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6483,22 +6503,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6583,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6602,17 +6622,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6682,7 +6702,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6721,17 +6741,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6797,7 +6817,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6851,7 +6871,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6916,7 +6936,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6970,7 +6990,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7035,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7089,7 +7109,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7154,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7193,7 +7213,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7208,7 +7228,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7246,19 +7266,19 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
@@ -7273,7 +7293,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7312,22 +7332,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>85.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7355,32 +7375,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7388,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7412,37 +7436,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7470,32 +7494,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:54</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7503,7 +7531,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7527,37 +7555,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7585,32 +7613,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:03</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7618,7 +7650,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7642,37 +7674,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7700,32 +7732,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7733,7 +7769,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7757,32 +7793,32 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7848,7 +7884,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7887,7 +7923,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7926,32 +7962,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7959,7 +7999,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -7983,33 +8023,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB64" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8114,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8124,7 +8168,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8152,32 +8196,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8185,7 +8233,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8209,32 +8257,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8300,7 +8348,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8411,7 +8459,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8465,7 +8513,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8574,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8580,7 +8628,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8641,7 +8689,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8695,7 +8743,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8756,7 +8804,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8810,7 +8858,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8818,22 +8866,22 @@
       <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A51173D</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -8866,12 +8914,12 @@
       <c r="M72" s="2" t="inlineStr"/>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:50</t>
         </is>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8910,22 +8958,1168 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
+      <c r="AA73" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB72" s="2" t="inlineStr">
+      <c r="AB73" s="2" t="inlineStr">
         <is>
           <t>83.2</t>
         </is>
       </c>
-      <c r="AC72" s="2" t="inlineStr">
-        <is>
-          <t>5/18</t>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>85.6</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr"/>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,22 +1180,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,22 +1648,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,22 +2120,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2465,18 +2465,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2541,7 +2545,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2595,7 +2599,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2699,7 +2703,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2714,7 +2718,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2779,7 +2783,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2818,7 +2822,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2894,7 +2898,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2933,22 +2937,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3009,7 +3013,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3048,22 +3052,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3124,7 +3128,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3178,7 +3182,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3247,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3282,7 +3286,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3297,7 +3301,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3416,7 +3420,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3481,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3531,7 +3535,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3596,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3646,7 +3650,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3711,7 +3715,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3750,22 +3754,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3834,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3869,22 +3873,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3953,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4068,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4107,22 +4111,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4191,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4241,7 +4245,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4306,7 +4310,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4345,7 +4349,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4360,7 +4364,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4429,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4479,7 +4483,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4583,7 +4587,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4659,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4710,22 +4714,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4790,7 +4794,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4829,22 +4833,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4913,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4948,7 +4952,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4963,7 +4967,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5028,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5075,22 +5079,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5155,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5209,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5274,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5328,7 +5332,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5393,7 +5397,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5447,7 +5451,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5516,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5631,7 +5635,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5685,7 +5689,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5750,7 +5754,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5789,22 +5793,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5908,22 +5912,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5988,7 +5992,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6027,7 +6031,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6107,7 +6111,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6161,7 +6165,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6230,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6265,7 +6269,7 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA49" s="2" t="inlineStr">
@@ -6280,7 +6284,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6345,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6399,7 +6403,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6468,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6518,7 +6522,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6583,7 +6587,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6702,7 +6706,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6756,7 +6760,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6821,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6856,22 +6860,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6936,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6975,22 +6979,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7055,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7094,7 +7098,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7174,7 +7178,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7228,7 +7232,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7293,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7332,7 +7336,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7347,7 +7351,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7416,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7466,7 +7470,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7531,7 +7535,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7585,7 +7589,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7650,7 +7654,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7704,7 +7708,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7769,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7884,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7999,7 +8003,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8053,7 +8057,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8081,32 +8085,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8114,7 +8122,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8138,37 +8146,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>97.3</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8218,12 +8226,12 @@
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N66" s="2" t="inlineStr">
@@ -8233,7 +8241,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8287,7 +8295,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8315,32 +8323,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -8348,7 +8360,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8372,33 +8384,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8426,32 +8442,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -8459,7 +8479,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8483,37 +8503,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8541,32 +8561,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8574,7 +8598,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8598,37 +8622,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8689,7 +8713,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8728,7 +8752,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8743,7 +8767,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8771,32 +8795,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8804,7 +8832,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8828,37 +8856,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8886,32 +8914,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8919,7 +8951,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8943,37 +8975,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9034,7 +9066,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9073,7 +9105,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9149,7 +9181,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9203,7 +9235,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9264,7 +9296,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9303,7 +9335,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9318,7 +9350,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9379,7 +9411,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9433,7 +9465,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9494,7 +9526,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9548,7 +9580,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9609,7 +9641,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9663,7 +9695,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9724,7 +9756,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9839,7 +9871,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9950,7 +9982,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10004,7 +10036,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10065,7 +10097,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10119,7 +10151,1042 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>97.3</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:10</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>85.6</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -942,22 +942,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1882,22 +1882,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2001,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2235,18 +2235,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2355,17 +2359,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2465,7 +2469,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2545,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,22 +2588,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2718,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2783,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2837,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2898,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2937,7 +2941,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -2952,7 +2956,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3013,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3067,7 +3071,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3128,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3167,22 +3171,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3291,17 +3295,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3420,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3481,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3520,22 +3524,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3600,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3640,17 +3644,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3769,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3888,7 +3892,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3992,22 +3996,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4072,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4191,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4230,22 +4234,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4364,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4429,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4473,17 +4477,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4602,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4663,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4714,7 +4718,7 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA36" s="2" t="inlineStr">
@@ -4729,7 +4733,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4794,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4848,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4913,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4957,17 +4961,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5094,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5159,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5198,22 +5202,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5317,22 +5321,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5397,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5441,17 +5445,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5516,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5555,22 +5559,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5635,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5679,17 +5683,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5808,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5873,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5927,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5992,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6046,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6150,22 +6154,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6274,17 +6278,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6349,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6393,17 +6397,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6468,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6507,22 +6511,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6587,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6626,22 +6630,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6706,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6750,17 +6754,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6821,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6875,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6994,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7059,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7113,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7178,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7217,22 +7221,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7297,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7341,17 +7345,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7416,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7455,22 +7459,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7539,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,17 +7583,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7654,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7693,22 +7697,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7812,22 +7816,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7888,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7927,18 +7931,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB63" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8042,22 +8050,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8122,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8176,7 +8184,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8285,17 +8293,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8399,7 +8407,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8479,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8533,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8598,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8637,7 +8645,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8652,7 +8660,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8767,7 +8775,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8886,7 +8894,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9005,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9066,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9120,7 +9128,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9148,32 +9156,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9181,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9205,37 +9217,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9263,32 +9275,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9296,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9320,17 +9336,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9340,17 +9356,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9378,32 +9394,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9411,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9435,37 +9455,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9493,32 +9513,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9526,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9550,37 +9574,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9608,32 +9632,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:01</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9641,7 +9669,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9665,17 +9693,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9685,17 +9713,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9723,32 +9751,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9756,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9780,37 +9812,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9838,32 +9870,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9871,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9895,33 +9931,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB80" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -9949,32 +9989,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9982,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10006,17 +10050,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10026,17 +10070,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10064,32 +10108,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -10097,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10121,37 +10169,37 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10212,7 +10260,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10266,7 +10314,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -10327,7 +10375,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10366,7 +10414,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10442,7 +10490,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10496,7 +10544,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10605,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10596,7 +10644,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10611,7 +10659,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10720,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10726,7 +10774,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10835,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10841,7 +10889,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10902,7 +10950,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10956,7 +11004,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11017,7 +11065,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11061,17 +11109,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>85.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11132,7 +11180,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11186,7 +11234,927 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>77.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,17 +1767,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2006,17 +2006,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2125,17 +2125,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2474,17 +2474,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2588,7 +2588,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2603,7 +2603,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,22 +2707,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3017,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3061,17 +3061,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3295,17 +3295,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3534,12 +3534,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3758,17 +3758,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4076,7 +4076,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,17 +4120,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4239,17 +4239,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4353,22 +4353,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4552,7 +4552,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4798,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4842,17 +4842,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5083,17 +5083,17 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5326,17 +5326,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5921,17 +5921,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,17 +6278,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6516,17 +6516,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6825,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6869,17 +6869,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6988,17 +6988,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7063,7 +7063,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7301,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7345,17 +7345,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7474,7 +7474,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7702,17 +7702,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8169,17 +8169,17 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8249,7 +8249,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8298,12 +8298,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8412,17 +8412,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8487,7 +8487,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8531,17 +8531,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8650,17 +8650,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8760,22 +8760,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8884,17 +8884,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8998,17 +8998,17 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9074,7 +9074,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9312,7 +9312,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9356,17 +9356,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9470,7 +9470,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9485,7 +9485,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9594,17 +9594,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9961,7 +9961,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9999,12 +9999,12 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>107分钟</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
@@ -10026,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10075,12 +10075,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10118,24 +10118,24 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>94分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10194,12 +10194,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10227,32 +10227,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10260,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10284,32 +10288,32 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>97.3</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10342,32 +10346,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -10375,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10399,17 +10407,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10419,17 +10427,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10457,32 +10465,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:10</t>
@@ -10490,7 +10502,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10514,17 +10526,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10534,17 +10546,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>92.4</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10572,32 +10584,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10605,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10629,17 +10645,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10649,17 +10665,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10687,32 +10703,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:03</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10720,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10744,37 +10764,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>91.7</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10802,32 +10822,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10835,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10859,17 +10883,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10879,17 +10903,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10974,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11004,7 +11028,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11032,32 +11056,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11065,7 +11093,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11089,17 +11117,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11109,17 +11137,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11147,32 +11175,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:27</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -11180,7 +11212,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11204,32 +11236,32 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11262,32 +11294,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11295,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11319,17 +11355,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11339,17 +11375,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>88.1</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11464,7 +11500,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11525,7 +11561,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11564,7 +11600,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11579,7 +11615,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11640,7 +11676,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11694,7 +11730,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11755,7 +11791,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11809,7 +11845,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11906,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11914,17 +11950,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>77.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11985,7 +12021,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12034,12 +12070,12 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -12100,7 +12136,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12144,15 +12180,475 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
         <is>
           <t>11/18</t>
         </is>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -903,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1185,17 +1185,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,17 +1648,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2011,12 +2011,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2240,17 +2240,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2474,17 +2474,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2593,17 +2593,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2946,17 +2946,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3524,22 +3524,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3877,17 +3877,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4244,12 +4244,12 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4368,7 +4368,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4723,17 +4723,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,17 +7464,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7658,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7831,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7892,7 +7892,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7936,17 +7936,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8050,22 +8050,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8169,17 +8169,17 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8368,7 +8368,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8412,17 +8412,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8650,17 +8650,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8775,7 +8775,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9013,7 +9013,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9193,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9475,17 +9475,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9550,7 +9550,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9723,7 +9723,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9907,7 +9907,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9951,17 +9951,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10184,22 +10184,22 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10303,17 +10303,17 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10427,17 +10427,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -10621,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10665,17 +10665,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10779,7 +10779,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10794,7 +10794,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11028,7 +11028,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11304,12 +11304,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>19:36</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -11331,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11380,12 +11380,12 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>88.1</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11500,7 +11500,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11528,32 +11528,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -11561,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11585,17 +11589,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11605,17 +11609,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11643,32 +11647,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11676,7 +11684,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11700,17 +11708,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11720,17 +11728,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11791,7 +11799,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11845,7 +11853,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11873,32 +11881,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11906,7 +11918,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11930,17 +11942,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11950,17 +11962,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -11988,32 +12000,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:17</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12021,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12045,37 +12061,37 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12119,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12136,7 +12156,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12160,17 +12180,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12180,17 +12200,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12218,32 +12238,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12251,7 +12275,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12275,32 +12299,32 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA100" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>95.4</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12366,7 +12390,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12420,7 +12444,7 @@
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -12481,7 +12505,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12520,7 +12544,7 @@
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
@@ -12535,7 +12559,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -12596,7 +12620,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12640,17 +12664,362 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>83.7</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>95.4</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>91.7</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -957,7 +957,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1190,12 +1190,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,17 +1772,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2369,7 +2369,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2593,17 +2593,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2902,7 +2902,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3186,7 +3186,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3424,7 +3424,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3763,17 +3763,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3887,7 +3887,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4011,7 +4011,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4249,7 +4249,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4358,17 +4358,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4487,7 +4487,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4852,7 +4852,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4971,7 +4971,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5032,7 +5032,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5088,17 +5088,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5217,7 +5217,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5336,7 +5336,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6526,7 +6526,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6645,7 +6645,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6764,7 +6764,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7236,7 +7236,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,17 +7464,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7831,7 +7831,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7946,7 +7946,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8303,7 +8303,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8606,7 +8606,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8655,12 +8655,12 @@
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8765,17 +8765,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8959,7 +8959,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,17 +9003,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9247,7 +9247,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9475,17 +9475,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9604,7 +9604,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9842,7 +9842,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10080,7 +10080,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10621,7 +10621,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10670,12 +10670,12 @@
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10784,17 +10784,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10913,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11147,7 +11147,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11256,17 +11256,17 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11385,7 +11385,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11500,7 +11500,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11609,17 +11609,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11738,7 +11738,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11853,7 +11853,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12129,24 +12129,24 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N99" s="2" t="inlineStr">
@@ -12156,7 +12156,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12205,12 +12205,12 @@
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12248,24 +12248,24 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12275,7 +12275,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12324,7 +12324,7 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
@@ -12357,32 +12357,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12390,7 +12394,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12414,17 +12418,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12434,17 +12438,17 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -12472,32 +12476,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:16</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12505,7 +12513,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12529,17 +12537,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12549,17 +12557,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12587,32 +12595,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:29</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -12620,7 +12632,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12644,17 +12656,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12664,17 +12676,17 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12735,7 +12747,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12850,7 +12862,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12899,7 +12911,7 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>95.4</t>
+          <t>95.8</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
@@ -12965,7 +12977,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13009,17 +13021,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>91.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-28-浦东78路.xlsx
+++ b/data/export/2026-09-28-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,7 +718,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -1076,7 +1076,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -2484,7 +2484,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2549,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3529,17 +3529,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3882,17 +3882,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -4314,7 +4314,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6879,7 +6879,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -7117,7 +7117,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7469,7 +7469,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8055,17 +8055,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8174,17 +8174,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8541,7 +8541,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -8721,7 +8721,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9431,7 +9431,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -10145,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10189,17 +10189,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10308,17 +10308,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10437,7 +10437,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10556,7 +10556,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -10740,7 +10740,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11614,7 +11614,7 @@
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11972,7 +11972,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -12037,7 +12037,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12081,17 +12081,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -12275,7 +12275,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12319,17 +12319,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12513,7 +12513,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12605,24 +12605,24 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>21:29</t>
+          <t>21:31</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N103" s="2" t="inlineStr">
@@ -12632,7 +12632,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12681,7 +12681,7 @@
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
@@ -12714,32 +12714,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:48</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -12747,7 +12751,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:40</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12771,17 +12775,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12791,17 +12795,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -12829,32 +12833,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:23</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12862,7 +12870,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12886,17 +12894,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12906,17 +12914,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>95.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12977,7 +12985,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
